--- a/auction-data/by-sale-date/2026-06-15.xlsx
+++ b/auction-data/by-sale-date/2026-06-15.xlsx
@@ -7,7 +7,7 @@
     <sheet name="요약" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'경매목록'!A1:M162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'경매목록'!A1:M154</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M162"/>
+  <dimension ref="A1:M154"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -4084,25 +4084,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C90" t="str">
-        <v>서울동부지방법원 2025타경51837</v>
+        <v>서울동부지방법원 2025타경51853</v>
       </c>
       <c r="D90" t="str">
         <v>1</v>
       </c>
       <c r="E90" t="str">
-        <v>서울특별시 강동구 둔촌동 518-2 광남아파트 3층302호</v>
+        <v>서울특별시 강동구 길동 415-16 청광플러스원큐브3차 5층507호</v>
       </c>
       <c r="F90">
-        <v>84.63</v>
+        <v>17.689</v>
       </c>
       <c r="G90">
-        <v>25.6</v>
+        <v>5.4</v>
       </c>
       <c r="H90">
-        <v>760000000</v>
+        <v>119000000</v>
       </c>
       <c r="I90">
-        <v>760000000</v>
+        <v>119000000</v>
       </c>
       <c r="J90">
         <v>100</v>
@@ -4125,25 +4125,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C91" t="str">
-        <v>서울동부지방법원 2025타경51853</v>
+        <v>서울동부지방법원 2025타경51861</v>
       </c>
       <c r="D91" t="str">
         <v>1</v>
       </c>
       <c r="E91" t="str">
-        <v>서울특별시 강동구 길동 415-16 청광플러스원큐브3차 5층507호</v>
+        <v>서울특별시 광진구 중곡동 639-4 정익제이타워1차 8층811호</v>
       </c>
       <c r="F91">
-        <v>17.689</v>
+        <v>16.37</v>
       </c>
       <c r="G91">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="H91">
-        <v>119000000</v>
+        <v>194000000</v>
       </c>
       <c r="I91">
-        <v>119000000</v>
+        <v>194000000</v>
       </c>
       <c r="J91">
         <v>100</v>
@@ -4166,25 +4166,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C92" t="str">
-        <v>서울동부지방법원 2025타경51861</v>
+        <v>서울동부지방법원 2025타경51871</v>
       </c>
       <c r="D92" t="str">
         <v>1</v>
       </c>
       <c r="E92" t="str">
-        <v>서울특별시 광진구 중곡동 639-4 정익제이타워1차 8층811호</v>
+        <v>서울특별시 성동구 용답동 229-1 동우리즈힐스 7층708호</v>
       </c>
       <c r="F92">
-        <v>16.37</v>
+        <v>16.67</v>
       </c>
       <c r="G92">
         <v>5</v>
       </c>
       <c r="H92">
-        <v>194000000</v>
+        <v>201000000</v>
       </c>
       <c r="I92">
-        <v>194000000</v>
+        <v>201000000</v>
       </c>
       <c r="J92">
         <v>100</v>
@@ -4207,25 +4207,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C93" t="str">
-        <v>서울동부지방법원 2025타경51871</v>
+        <v>서울동부지방법원 2025타경51893</v>
       </c>
       <c r="D93" t="str">
         <v>1</v>
       </c>
       <c r="E93" t="str">
-        <v>서울특별시 성동구 용답동 229-1 동우리즈힐스 7층708호</v>
+        <v>서울특별시 송파구 거여동 35-2 아키스오피스텔 6층602호</v>
       </c>
       <c r="F93">
-        <v>16.67</v>
+        <v>42.56</v>
       </c>
       <c r="G93">
-        <v>5</v>
+        <v>12.9</v>
       </c>
       <c r="H93">
-        <v>201000000</v>
+        <v>252000000</v>
       </c>
       <c r="I93">
-        <v>201000000</v>
+        <v>252000000</v>
       </c>
       <c r="J93">
         <v>100</v>
@@ -4237,7 +4237,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="M93" t="str">
-        <v/>
+        <v>토지 별도 등기 있음</v>
       </c>
     </row>
     <row r="94">
@@ -4248,25 +4248,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C94" t="str">
-        <v>서울동부지방법원 2025타경51893</v>
+        <v>서울동부지방법원 2025타경51926</v>
       </c>
       <c r="D94" t="str">
         <v>1</v>
       </c>
       <c r="E94" t="str">
-        <v>서울특별시 송파구 거여동 35-2 아키스오피스텔 6층602호</v>
+        <v>서울특별시 송파구 거여동 17-19</v>
       </c>
       <c r="F94">
-        <v>42.56</v>
+        <v>126</v>
       </c>
       <c r="G94">
-        <v>12.9</v>
+        <v>38.1</v>
       </c>
       <c r="H94">
-        <v>252000000</v>
+        <v>1688400000</v>
       </c>
       <c r="I94">
-        <v>252000000</v>
+        <v>1688400000</v>
       </c>
       <c r="J94">
         <v>100</v>
@@ -4278,10 +4278,10 @@
         <v>2026-06-15</v>
       </c>
       <c r="M94" t="str">
-        <v>토지 별도 등기 있음</v>
-      </c>
-    </row>
-    <row r="95" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
       <c r="A95" t="str">
         <v>서울</v>
       </c>
@@ -4289,25 +4289,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C95" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경51928</v>
       </c>
       <c r="D95" t="str">
         <v>1</v>
       </c>
       <c r="E95" t="str">
-        <v>서울특별시 송파구 석촌동 268-5</v>
+        <v>서울특별시 송파구 송파동 85 에스아이팰리스레이크잠실 6층601호</v>
       </c>
       <c r="F95">
-        <v>170.3</v>
+        <v>27.33</v>
       </c>
       <c r="G95">
-        <v>51.5</v>
+        <v>8.3</v>
       </c>
       <c r="H95">
-        <v>2528000000</v>
+        <v>434000000</v>
       </c>
       <c r="I95">
-        <v>2528000000</v>
+        <v>434000000</v>
       </c>
       <c r="J95">
         <v>100</v>
@@ -4318,12 +4318,11 @@
       <c r="L95" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M95" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="96" xml:space="preserve">
+      <c r="M95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
       <c r="A96" t="str">
         <v>서울</v>
       </c>
@@ -4331,25 +4330,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C96" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경51938</v>
       </c>
       <c r="D96" t="str">
         <v>1</v>
       </c>
       <c r="E96" t="str">
-        <v>서울특별시 송파구 석촌동 268-5 2층201호</v>
+        <v>서울특별시 강동구 암사동 491-22 삼정하우스 3층303호</v>
       </c>
       <c r="F96">
-        <v>11.4</v>
+        <v>41.56</v>
       </c>
       <c r="G96">
-        <v>3.4</v>
+        <v>12.6</v>
       </c>
       <c r="H96">
-        <v>2528000000</v>
+        <v>420000000</v>
       </c>
       <c r="I96">
-        <v>2528000000</v>
+        <v>420000000</v>
       </c>
       <c r="J96">
         <v>100</v>
@@ -4360,12 +4359,11 @@
       <c r="L96" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M96" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="97" xml:space="preserve">
+      <c r="M96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
       <c r="A97" t="str">
         <v>서울</v>
       </c>
@@ -4373,25 +4371,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C97" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경51944</v>
       </c>
       <c r="D97" t="str">
         <v>1</v>
       </c>
       <c r="E97" t="str">
-        <v>서울특별시 송파구 석촌동 268-5 2층202호</v>
+        <v>서울특별시 광진구 중곡동 56-18 3층303호</v>
       </c>
       <c r="F97">
-        <v>46.96</v>
+        <v>29.42</v>
       </c>
       <c r="G97">
-        <v>14.2</v>
+        <v>8.9</v>
       </c>
       <c r="H97">
-        <v>2528000000</v>
+        <v>337000000</v>
       </c>
       <c r="I97">
-        <v>2528000000</v>
+        <v>337000000</v>
       </c>
       <c r="J97">
         <v>100</v>
@@ -4402,12 +4400,11 @@
       <c r="L97" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M97" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="98" xml:space="preserve">
+      <c r="M97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
       <c r="A98" t="str">
         <v>서울</v>
       </c>
@@ -4415,25 +4412,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C98" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경51965</v>
       </c>
       <c r="D98" t="str">
         <v>1</v>
       </c>
       <c r="E98" t="str">
-        <v>서울특별시 송파구 석촌동 268-5 3층301호</v>
+        <v>서울특별시 강동구 길동 387-5 길동청광플러스원큐브1차 9층910호</v>
       </c>
       <c r="F98">
-        <v>43.49</v>
+        <v>16.685</v>
       </c>
       <c r="G98">
-        <v>13.2</v>
+        <v>5</v>
       </c>
       <c r="H98">
-        <v>2528000000</v>
+        <v>109000000</v>
       </c>
       <c r="I98">
-        <v>2528000000</v>
+        <v>109000000</v>
       </c>
       <c r="J98">
         <v>100</v>
@@ -4444,12 +4441,11 @@
       <c r="L98" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M98" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="99" xml:space="preserve">
+      <c r="M98" t="str">
+        <v>건축물현황도[평면도(9층)]와 건축물현황도[평면도(910호)]는 불일치 (좌우반전)</v>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" t="str">
         <v>서울</v>
       </c>
@@ -4457,25 +4453,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C99" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경52003</v>
       </c>
       <c r="D99" t="str">
         <v>1</v>
       </c>
       <c r="E99" t="str">
-        <v>서울특별시 송파구 석촌동 268-5 3층302호</v>
+        <v>서울특별시 송파구 송파동 85 에스아이팰리스레이크잠실 8층804호</v>
       </c>
       <c r="F99">
-        <v>46.96</v>
+        <v>19.7</v>
       </c>
       <c r="G99">
-        <v>14.2</v>
+        <v>6</v>
       </c>
       <c r="H99">
-        <v>2528000000</v>
+        <v>454000000</v>
       </c>
       <c r="I99">
-        <v>2528000000</v>
+        <v>454000000</v>
       </c>
       <c r="J99">
         <v>100</v>
@@ -4486,12 +4482,11 @@
       <c r="L99" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M99" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="100" xml:space="preserve">
+      <c r="M99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" t="str">
         <v>서울</v>
       </c>
@@ -4499,25 +4494,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C100" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경52025</v>
       </c>
       <c r="D100" t="str">
         <v>1</v>
       </c>
       <c r="E100" t="str">
-        <v>서울특별시 송파구 석촌동 268-5 4층401호</v>
+        <v>서울특별시 강동구 천호동 453-5 로데오팰리스 지1층비102호</v>
       </c>
       <c r="F100">
-        <v>65.25</v>
+        <v>97.13</v>
       </c>
       <c r="G100">
-        <v>19.7</v>
+        <v>29.4</v>
       </c>
       <c r="H100">
-        <v>2528000000</v>
+        <v>870000000</v>
       </c>
       <c r="I100">
-        <v>2528000000</v>
+        <v>870000000</v>
       </c>
       <c r="J100">
         <v>100</v>
@@ -4528,12 +4523,11 @@
       <c r="L100" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M100" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="101" xml:space="preserve">
+      <c r="M100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
       <c r="A101" t="str">
         <v>서울</v>
       </c>
@@ -4541,25 +4535,25 @@
         <v>서울동부지방법원</v>
       </c>
       <c r="C101" t="str">
-        <v>서울동부지방법원 2025타경51912</v>
+        <v>서울동부지방법원 2025타경52037</v>
       </c>
       <c r="D101" t="str">
         <v>1</v>
       </c>
       <c r="E101" t="str">
-        <v>서울특별시 송파구 석촌동 268-5 5층501호</v>
+        <v>서울특별시 송파구 송파동 85 에스아이팰리스레이크잠실 9층909호</v>
       </c>
       <c r="F101">
-        <v>51</v>
+        <v>19.7</v>
       </c>
       <c r="G101">
-        <v>15.4</v>
+        <v>6</v>
       </c>
       <c r="H101">
-        <v>2528000000</v>
+        <v>443000000</v>
       </c>
       <c r="I101">
-        <v>2528000000</v>
+        <v>443000000</v>
       </c>
       <c r="J101">
         <v>100</v>
@@ -4570,383 +4564,389 @@
       <c r="L101" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M101" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각
-대지권미등기이나, 토지는 건물의 대지사용권 있음</v>
-      </c>
-    </row>
-    <row r="102">
+      <c r="M101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
       <c r="A102" t="str">
-        <v>서울</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B102" t="str">
-        <v>서울동부지방법원</v>
+        <v>성남지원</v>
       </c>
       <c r="C102" t="str">
-        <v>서울동부지방법원 2025타경51926</v>
+        <v>성남지원 2022타경59047</v>
       </c>
       <c r="D102" t="str">
         <v>1</v>
       </c>
       <c r="E102" t="str">
-        <v>서울특별시 송파구 거여동 17-19</v>
+        <v>경기도 성남시 분당구 불정로 112 (정자동,피더하우스) 1층에이123호</v>
       </c>
       <c r="F102">
-        <v>126</v>
+        <v>61.43</v>
       </c>
       <c r="G102">
-        <v>38.1</v>
+        <v>18.6</v>
       </c>
       <c r="H102">
-        <v>1688400000</v>
+        <v>419000000</v>
       </c>
       <c r="I102">
-        <v>1688400000</v>
+        <v>419000000</v>
       </c>
       <c r="J102">
         <v>100</v>
       </c>
       <c r="K102" t="str">
-        <v>신건</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L102" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M102" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B103" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C103" t="str">
-        <v>서울동부지방법원 2025타경51928</v>
-      </c>
-      <c r="D103" t="str">
-        <v>1</v>
-      </c>
-      <c r="E103" t="str">
-        <v>서울특별시 송파구 송파동 85 에스아이팰리스레이크잠실 6층601호</v>
-      </c>
-      <c r="F103">
-        <v>27.33</v>
-      </c>
-      <c r="G103">
-        <v>8.3</v>
-      </c>
-      <c r="H103">
-        <v>434000000</v>
-      </c>
-      <c r="I103">
-        <v>434000000</v>
-      </c>
-      <c r="J103">
-        <v>100</v>
-      </c>
-      <c r="K103" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L103" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B104" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C104" t="str">
-        <v>서울동부지방법원 2025타경51938</v>
-      </c>
-      <c r="D104" t="str">
-        <v>1</v>
-      </c>
-      <c r="E104" t="str">
-        <v>서울특별시 강동구 암사동 491-22 삼정하우스 3층303호</v>
-      </c>
-      <c r="F104">
-        <v>41.56</v>
-      </c>
-      <c r="G104">
-        <v>12.6</v>
-      </c>
-      <c r="H104">
-        <v>420000000</v>
-      </c>
-      <c r="I104">
-        <v>420000000</v>
-      </c>
-      <c r="J104">
-        <v>100</v>
-      </c>
-      <c r="K104" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L104" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M104" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B105" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C105" t="str">
-        <v>서울동부지방법원 2025타경51944</v>
-      </c>
-      <c r="D105" t="str">
-        <v>1</v>
-      </c>
-      <c r="E105" t="str">
-        <v>서울특별시 광진구 중곡동 56-18 3층303호</v>
-      </c>
-      <c r="F105">
-        <v>29.42</v>
-      </c>
-      <c r="G105">
-        <v>8.9</v>
-      </c>
-      <c r="H105">
-        <v>337000000</v>
-      </c>
-      <c r="I105">
-        <v>337000000</v>
-      </c>
-      <c r="J105">
-        <v>100</v>
-      </c>
-      <c r="K105" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L105" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B106" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C106" t="str">
-        <v>서울동부지방법원 2025타경51965</v>
-      </c>
-      <c r="D106" t="str">
-        <v>1</v>
-      </c>
-      <c r="E106" t="str">
-        <v>서울특별시 강동구 길동 387-5 길동청광플러스원큐브1차 9층910호</v>
-      </c>
-      <c r="F106">
-        <v>16.685</v>
-      </c>
-      <c r="G106">
-        <v>5</v>
-      </c>
-      <c r="H106">
-        <v>109000000</v>
-      </c>
-      <c r="I106">
-        <v>109000000</v>
-      </c>
-      <c r="J106">
-        <v>100</v>
-      </c>
-      <c r="K106" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L106" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M106" t="str">
-        <v>건축물현황도[평면도(9층)]와 건축물현황도[평면도(910호)]는 불일치 (좌우반전)</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B107" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C107" t="str">
-        <v>서울동부지방법원 2025타경52003</v>
-      </c>
-      <c r="D107" t="str">
-        <v>1</v>
-      </c>
-      <c r="E107" t="str">
-        <v>서울특별시 송파구 송파동 85 에스아이팰리스레이크잠실 8층804호</v>
-      </c>
-      <c r="F107">
-        <v>19.7</v>
-      </c>
-      <c r="G107">
-        <v>6</v>
-      </c>
-      <c r="H107">
-        <v>454000000</v>
-      </c>
-      <c r="I107">
-        <v>454000000</v>
-      </c>
-      <c r="J107">
-        <v>100</v>
-      </c>
-      <c r="K107" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L107" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B108" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C108" t="str">
-        <v>서울동부지방법원 2025타경52025</v>
-      </c>
-      <c r="D108" t="str">
-        <v>1</v>
-      </c>
-      <c r="E108" t="str">
-        <v>서울특별시 강동구 천호동 453-5 로데오팰리스 지1층비102호</v>
-      </c>
-      <c r="F108">
-        <v>97.13</v>
-      </c>
-      <c r="G108">
-        <v>29.4</v>
-      </c>
-      <c r="H108">
-        <v>870000000</v>
-      </c>
-      <c r="I108">
-        <v>870000000</v>
-      </c>
-      <c r="J108">
-        <v>100</v>
-      </c>
-      <c r="K108" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L108" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M108" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>서울</v>
-      </c>
-      <c r="B109" t="str">
-        <v>서울동부지방법원</v>
-      </c>
-      <c r="C109" t="str">
-        <v>서울동부지방법원 2025타경52037</v>
-      </c>
-      <c r="D109" t="str">
-        <v>1</v>
-      </c>
-      <c r="E109" t="str">
-        <v>서울특별시 송파구 송파동 85 에스아이팰리스레이크잠실 9층909호</v>
-      </c>
-      <c r="F109">
-        <v>19.7</v>
-      </c>
-      <c r="G109">
-        <v>6</v>
-      </c>
-      <c r="H109">
-        <v>443000000</v>
-      </c>
-      <c r="I109">
-        <v>443000000</v>
-      </c>
-      <c r="J109">
-        <v>100</v>
-      </c>
-      <c r="K109" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L109" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M109" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="110" xml:space="preserve">
-      <c r="A110" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B110" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C110" t="str">
-        <v>성남지원 2022타경59047</v>
-      </c>
-      <c r="D110" t="str">
-        <v>1</v>
-      </c>
-      <c r="E110" t="str">
-        <v>경기도 성남시 분당구 불정로 112 (정자동,피더하우스) 1층에이123호</v>
-      </c>
-      <c r="F110">
-        <v>61.43</v>
-      </c>
-      <c r="G110">
-        <v>18.6</v>
-      </c>
-      <c r="H110">
-        <v>419000000</v>
-      </c>
-      <c r="I110">
-        <v>419000000</v>
-      </c>
-      <c r="J110">
-        <v>100</v>
-      </c>
-      <c r="K110" t="str">
-        <v>유찰 1회</v>
-      </c>
-      <c r="L110" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M110" t="str" xml:space="preserve">
+      <c r="M102" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 공부상 1층은 외형상 2층으로 본건 현관문에는 223호로 표시되어 있음.
 2. 본건 공부상 용도는 노유자시설(노인복지시설)로 입주자 제한여부는 개별확인요망.
 3. 선순위가등기권자 유철재는 담보가등기권자로  2025.1.17.자 권리신고 및 배당요구신청서를 제출함.</v>
       </c>
     </row>
-    <row r="111" xml:space="preserve">
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B103" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C103" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D103" t="str">
+        <v>1</v>
+      </c>
+      <c r="E103" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F103">
+        <v>472</v>
+      </c>
+      <c r="G103">
+        <v>142.8</v>
+      </c>
+      <c r="H103">
+        <v>3923726000</v>
+      </c>
+      <c r="I103">
+        <v>2746608000</v>
+      </c>
+      <c r="J103">
+        <v>70</v>
+      </c>
+      <c r="K103" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L103" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M103" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B104" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C104" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D104" t="str">
+        <v>1</v>
+      </c>
+      <c r="E104" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F104">
+        <v>308</v>
+      </c>
+      <c r="G104">
+        <v>93.2</v>
+      </c>
+      <c r="H104">
+        <v>3923726000</v>
+      </c>
+      <c r="I104">
+        <v>2746608000</v>
+      </c>
+      <c r="J104">
+        <v>70</v>
+      </c>
+      <c r="K104" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L104" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M104" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="105" xml:space="preserve">
+      <c r="A105" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B105" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C105" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D105" t="str">
+        <v>1</v>
+      </c>
+      <c r="E105" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F105">
+        <v>22</v>
+      </c>
+      <c r="G105">
+        <v>6.7</v>
+      </c>
+      <c r="H105">
+        <v>3923726000</v>
+      </c>
+      <c r="I105">
+        <v>2746608000</v>
+      </c>
+      <c r="J105">
+        <v>70</v>
+      </c>
+      <c r="K105" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L105" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M105" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B106" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C106" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D106" t="str">
+        <v>1</v>
+      </c>
+      <c r="E106" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F106">
+        <v>178</v>
+      </c>
+      <c r="G106">
+        <v>53.8</v>
+      </c>
+      <c r="H106">
+        <v>3923726000</v>
+      </c>
+      <c r="I106">
+        <v>2746608000</v>
+      </c>
+      <c r="J106">
+        <v>70</v>
+      </c>
+      <c r="K106" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L106" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M106" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="107" xml:space="preserve">
+      <c r="A107" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B107" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C107" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D107" t="str">
+        <v>1</v>
+      </c>
+      <c r="E107" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F107">
+        <v>330</v>
+      </c>
+      <c r="G107">
+        <v>99.8</v>
+      </c>
+      <c r="H107">
+        <v>3923726000</v>
+      </c>
+      <c r="I107">
+        <v>2746608000</v>
+      </c>
+      <c r="J107">
+        <v>70</v>
+      </c>
+      <c r="K107" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L107" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M107" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B108" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C108" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D108" t="str">
+        <v>1</v>
+      </c>
+      <c r="E108" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F108">
+        <v>472</v>
+      </c>
+      <c r="G108">
+        <v>142.8</v>
+      </c>
+      <c r="H108">
+        <v>3923726000</v>
+      </c>
+      <c r="I108">
+        <v>2746608000</v>
+      </c>
+      <c r="J108">
+        <v>70</v>
+      </c>
+      <c r="K108" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L108" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M108" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B109" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C109" t="str">
+        <v>성남지원 2023타경5542</v>
+      </c>
+      <c r="D109" t="str">
+        <v>1</v>
+      </c>
+      <c r="E109" t="str">
+        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+      </c>
+      <c r="F109">
+        <v>23</v>
+      </c>
+      <c r="G109">
+        <v>7</v>
+      </c>
+      <c r="H109">
+        <v>3923726000</v>
+      </c>
+      <c r="I109">
+        <v>2746608000</v>
+      </c>
+      <c r="J109">
+        <v>70</v>
+      </c>
+      <c r="K109" t="str">
+        <v>유찰 2회</v>
+      </c>
+      <c r="L109" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M109" t="str" xml:space="preserve">
+        <v xml:space="preserve">일괄매각_x000d_
+목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>성남 중원구</v>
+      </c>
+      <c r="B110" t="str">
+        <v>성남지원</v>
+      </c>
+      <c r="C110" t="str">
+        <v>성남지원 2023타경5818</v>
+      </c>
+      <c r="D110" t="str">
+        <v>1</v>
+      </c>
+      <c r="E110" t="str">
+        <v>경기도 성남시 중원구 시민로66번길 21 (중앙동,중앙동힐스테이트1차) 104동 13층1304호</v>
+      </c>
+      <c r="F110">
+        <v>120.97</v>
+      </c>
+      <c r="G110">
+        <v>36.6</v>
+      </c>
+      <c r="H110">
+        <v>959000000</v>
+      </c>
+      <c r="I110">
+        <v>959000000</v>
+      </c>
+      <c r="J110">
+        <v>100</v>
+      </c>
+      <c r="K110" t="str">
+        <v>신건</v>
+      </c>
+      <c r="L110" t="str">
+        <v>2026-06-15</v>
+      </c>
+      <c r="M110" t="str">
+        <v>신청채권자겸 가처분권자 강리원이 2026.02.25.자에 매각시 가처분 포기서류를 제출하겠다는 보정서 제출함.</v>
+      </c>
+    </row>
+    <row r="111">
       <c r="A111" t="str">
         <v>성남 중원구</v>
       </c>
@@ -4954,67 +4954,66 @@
         <v>성남지원</v>
       </c>
       <c r="C111" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2023타경58577</v>
       </c>
       <c r="D111" t="str">
         <v>1</v>
       </c>
       <c r="E111" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 중원구 둔촌대로80번길 3-10 (성남동,성남아리스타) 1층107호</v>
       </c>
       <c r="F111">
-        <v>472</v>
+        <v>24.938</v>
       </c>
       <c r="G111">
-        <v>142.8</v>
+        <v>7.5</v>
       </c>
       <c r="H111">
-        <v>3923726000</v>
+        <v>918000000</v>
       </c>
       <c r="I111">
-        <v>2746608000</v>
+        <v>918000000</v>
       </c>
       <c r="J111">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K111" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L111" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M111" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
-      </c>
-    </row>
-    <row r="112" xml:space="preserve">
+      <c r="M111" t="str">
+        <v>집합건축물대장상 용도는 제2종근린생활시설(일반음식점)이나 현재 공실상태임.</v>
+      </c>
+    </row>
+    <row r="112">
       <c r="A112" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B112" t="str">
         <v>성남지원</v>
       </c>
       <c r="C112" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2024타경3826</v>
       </c>
       <c r="D112" t="str">
         <v>1</v>
       </c>
       <c r="E112" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 분당구 야탑동 341 제지2층 제291호</v>
       </c>
       <c r="F112">
-        <v>308</v>
+        <v>10015.22</v>
       </c>
       <c r="G112">
-        <v>93.2</v>
+        <v>3029.6</v>
       </c>
       <c r="H112">
-        <v>3923726000</v>
+        <v>53000000</v>
       </c>
       <c r="I112">
-        <v>2746608000</v>
+        <v>37100000</v>
       </c>
       <c r="J112">
         <v>70</v>
@@ -5025,38 +5024,37 @@
       <c r="L112" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M112" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
-      </c>
-    </row>
-    <row r="113" xml:space="preserve">
+      <c r="M112" t="str">
+        <v>인접 호수와 함께 벽체구분 없이 이용중이며, 현재는 공실임.</v>
+      </c>
+    </row>
+    <row r="113">
       <c r="A113" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B113" t="str">
         <v>성남지원</v>
       </c>
       <c r="C113" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2024타경4324</v>
       </c>
       <c r="D113" t="str">
         <v>1</v>
       </c>
       <c r="E113" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 분당구 성남대로925번길 16 (야탑동,성남(분당)여객자동차터미널및복합건물) 지2층540호</v>
       </c>
       <c r="F113">
-        <v>22</v>
+        <v>4.94</v>
       </c>
       <c r="G113">
-        <v>6.7</v>
+        <v>1.5</v>
       </c>
       <c r="H113">
-        <v>3923726000</v>
+        <v>34000000</v>
       </c>
       <c r="I113">
-        <v>2746608000</v>
+        <v>23800000</v>
       </c>
       <c r="J113">
         <v>70</v>
@@ -5067,38 +5065,37 @@
       <c r="L113" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M113" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
-      </c>
-    </row>
-    <row r="114" xml:space="preserve">
+      <c r="M113" t="str">
+        <v>인접 호수와 함께 벽체구분 없이 이용중이며, 현재는 공실임.</v>
+      </c>
+    </row>
+    <row r="114">
       <c r="A114" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B114" t="str">
         <v>성남지원</v>
       </c>
       <c r="C114" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2024타경4409</v>
       </c>
       <c r="D114" t="str">
         <v>1</v>
       </c>
       <c r="E114" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 분당구 성남대로925번길 16 (야탑동,성남(분당)여객자동차터미널및복합건물) 지2층618호</v>
       </c>
       <c r="F114">
-        <v>178</v>
+        <v>7.29</v>
       </c>
       <c r="G114">
-        <v>53.8</v>
+        <v>2.2</v>
       </c>
       <c r="H114">
-        <v>3923726000</v>
+        <v>39000000</v>
       </c>
       <c r="I114">
-        <v>2746608000</v>
+        <v>27300000</v>
       </c>
       <c r="J114">
         <v>70</v>
@@ -5109,135 +5106,132 @@
       <c r="L114" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M114" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      <c r="M114" t="str">
+        <v>인접 호수와 함께 벽체구분 없이 이용중이며, 현재는 공실임.</v>
       </c>
     </row>
     <row r="115" xml:space="preserve">
       <c r="A115" t="str">
-        <v>성남 중원구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B115" t="str">
         <v>성남지원</v>
       </c>
       <c r="C115" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2024타경7156</v>
       </c>
       <c r="D115" t="str">
         <v>1</v>
       </c>
       <c r="E115" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 수정구 고등동 527-54</v>
       </c>
       <c r="F115">
-        <v>330</v>
+        <v>662</v>
       </c>
       <c r="G115">
-        <v>99.8</v>
+        <v>200.3</v>
       </c>
       <c r="H115">
-        <v>3923726000</v>
+        <v>43423440</v>
       </c>
       <c r="I115">
-        <v>2746608000</v>
+        <v>7298000</v>
       </c>
       <c r="J115">
-        <v>70</v>
+        <v>16.8</v>
       </c>
       <c r="K115" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 5회</v>
       </c>
       <c r="L115" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M115" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
-      </c>
-    </row>
-    <row r="116" xml:space="preserve">
+        <v xml:space="preserve">1. 공유자의 우선매수신고는 1회에 한하여 행사할 수 있음(공유자가 우선매수권 신고 후 매각기일까지 매수보증금을 미납하여 실효되는 경우에는 그 공유자는 이후 매각기일부터는 우선매수권을 행사할 수 없음).
+2. 재매각, 매수보증금은 최저매각가격의 20%임.</v>
+      </c>
+    </row>
+    <row r="116">
       <c r="A116" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B116" t="str">
         <v>성남지원</v>
       </c>
       <c r="C116" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2024타경66599</v>
       </c>
       <c r="D116" t="str">
         <v>1</v>
       </c>
       <c r="E116" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 분당구 성남대로925번길 16 (야탑동,성남(분당)여객자동차터미널및복합건물) 3층103호</v>
       </c>
       <c r="F116">
-        <v>472</v>
+        <v>49.83</v>
       </c>
       <c r="G116">
-        <v>142.8</v>
+        <v>15.1</v>
       </c>
       <c r="H116">
-        <v>3923726000</v>
+        <v>739000000</v>
       </c>
       <c r="I116">
-        <v>2746608000</v>
+        <v>177434000</v>
       </c>
       <c r="J116">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="K116" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 5회</v>
       </c>
       <c r="L116" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M116" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
-      </c>
-    </row>
-    <row r="117" xml:space="preserve">
+      <c r="M116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
       <c r="A117" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B117" t="str">
         <v>성남지원</v>
       </c>
       <c r="C117" t="str">
-        <v>성남지원 2023타경5542</v>
+        <v>성남지원 2024타경67486</v>
       </c>
       <c r="D117" t="str">
         <v>1</v>
       </c>
       <c r="E117" t="str">
-        <v>경기도 성남시 중원구 갈현동 293^297^290-2^297-1^292^292-1^297-2</v>
+        <v>경기도 성남시 분당구 성남대로925번길 16</v>
       </c>
       <c r="F117">
-        <v>23</v>
+        <v>48.26</v>
       </c>
       <c r="G117">
-        <v>7</v>
+        <v>14.6</v>
       </c>
       <c r="H117">
-        <v>3923726000</v>
+        <v>611000000</v>
       </c>
       <c r="I117">
-        <v>2746608000</v>
+        <v>209573000</v>
       </c>
       <c r="J117">
-        <v>70</v>
+        <v>34.3</v>
       </c>
       <c r="K117" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 4회</v>
       </c>
       <c r="L117" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M117" t="str" xml:space="preserve">
-        <v xml:space="preserve">일괄매각_x000d_
-목록4는 지목 "전"이나 현황 "도로"이며 농지취득자격증명 불요</v>
+      <c r="M117" t="str">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -5248,78 +5242,78 @@
         <v>성남지원</v>
       </c>
       <c r="C118" t="str">
-        <v>성남지원 2023타경5818</v>
+        <v>성남지원 2025타경442</v>
       </c>
       <c r="D118" t="str">
         <v>1</v>
       </c>
       <c r="E118" t="str">
-        <v>경기도 성남시 중원구 시민로66번길 21 (중앙동,중앙동힐스테이트1차) 104동 13층1304호</v>
+        <v>경기도 성남시 중원구 도촌동 산9</v>
       </c>
       <c r="F118">
-        <v>120.97</v>
+        <v>11901</v>
       </c>
       <c r="G118">
-        <v>36.6</v>
+        <v>3600.1</v>
       </c>
       <c r="H118">
-        <v>959000000</v>
+        <v>1713744000</v>
       </c>
       <c r="I118">
-        <v>959000000</v>
+        <v>411471000</v>
       </c>
       <c r="J118">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="K118" t="str">
-        <v>신건</v>
+        <v>유찰 5회</v>
       </c>
       <c r="L118" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M118" t="str">
-        <v>신청채권자겸 가처분권자 강리원이 2026.02.25.자에 매각시 가처분 포기서류를 제출하겠다는 보정서 제출함.</v>
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B119" t="str">
         <v>성남지원</v>
       </c>
       <c r="C119" t="str">
-        <v>성남지원 2023타경58577</v>
+        <v>성남지원 2025타경503</v>
       </c>
       <c r="D119" t="str">
         <v>1</v>
       </c>
       <c r="E119" t="str">
-        <v>경기도 성남시 중원구 둔촌대로80번길 3-10 (성남동,성남아리스타) 1층107호</v>
+        <v>경기도 성남시 분당구 서현동 275 라포르테블랑서현 605호</v>
       </c>
       <c r="F119">
-        <v>24.938</v>
+        <v>28.5058</v>
       </c>
       <c r="G119">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="H119">
-        <v>918000000</v>
+        <v>1245900000</v>
       </c>
       <c r="I119">
-        <v>918000000</v>
+        <v>610491000</v>
       </c>
       <c r="J119">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="K119" t="str">
-        <v>유찰 1회</v>
+        <v>유찰 3회</v>
       </c>
       <c r="L119" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M119" t="str">
-        <v>집합건축물대장상 용도는 제2종근린생활시설(일반음식점)이나 현재 공실상태임.</v>
+        <v>일괄매각</v>
       </c>
     </row>
     <row r="120">
@@ -5330,107 +5324,107 @@
         <v>성남지원</v>
       </c>
       <c r="C120" t="str">
-        <v>성남지원 2024타경3826</v>
+        <v>성남지원 2025타경503</v>
       </c>
       <c r="D120" t="str">
         <v>1</v>
       </c>
       <c r="E120" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 제지2층 제291호</v>
+        <v>경기도 성남시 분당구 서현동 275 라포르테블랑서현 제1주차장호</v>
       </c>
       <c r="F120">
-        <v>10015.22</v>
+        <v>3197.0632</v>
       </c>
       <c r="G120">
-        <v>3029.6</v>
+        <v>967.1</v>
       </c>
       <c r="H120">
-        <v>53000000</v>
+        <v>1245900000</v>
       </c>
       <c r="I120">
-        <v>37100000</v>
+        <v>610491000</v>
       </c>
       <c r="J120">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="K120" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 3회</v>
       </c>
       <c r="L120" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M120" t="str">
-        <v>인접 호수와 함께 벽체구분 없이 이용중이며, 현재는 공실임.</v>
+        <v>일괄매각</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>성남 분당구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B121" t="str">
         <v>성남지원</v>
       </c>
       <c r="C121" t="str">
-        <v>성남지원 2024타경4324</v>
+        <v>성남지원 2025타경930</v>
       </c>
       <c r="D121" t="str">
         <v>1</v>
       </c>
       <c r="E121" t="str">
-        <v>경기도 성남시 분당구 성남대로925번길 16 (야탑동,성남(분당)여객자동차터미널및복합건물) 지2층540호</v>
+        <v>경기도 성남시 수정구 사송동 산89</v>
       </c>
       <c r="F121">
-        <v>4.94</v>
+        <v>1915</v>
       </c>
       <c r="G121">
-        <v>1.5</v>
+        <v>579.3</v>
       </c>
       <c r="H121">
-        <v>34000000</v>
+        <v>1419015000</v>
       </c>
       <c r="I121">
-        <v>23800000</v>
+        <v>340706000</v>
       </c>
       <c r="J121">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="K121" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 5회</v>
       </c>
       <c r="L121" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M121" t="str">
-        <v>인접 호수와 함께 벽체구분 없이 이용중이며, 현재는 공실임.</v>
+        <v>지적도상 지목 도로와 접했으나. 현황은 자연림,맹지임.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>성남 분당구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B122" t="str">
         <v>성남지원</v>
       </c>
       <c r="C122" t="str">
-        <v>성남지원 2024타경4409</v>
+        <v>성남지원 2025타경2226</v>
       </c>
       <c r="D122" t="str">
         <v>1</v>
       </c>
       <c r="E122" t="str">
-        <v>경기도 성남시 분당구 성남대로925번길 16 (야탑동,성남(분당)여객자동차터미널및복합건물) 지2층618호</v>
+        <v>경기도 성남시 중원구 성남동 3499 니즈몰 1층1011호</v>
       </c>
       <c r="F122">
-        <v>7.29</v>
+        <v>3.74</v>
       </c>
       <c r="G122">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H122">
-        <v>39000000</v>
+        <v>47000000</v>
       </c>
       <c r="I122">
-        <v>27300000</v>
+        <v>32900000</v>
       </c>
       <c r="J122">
         <v>70</v>
@@ -5442,125 +5436,124 @@
         <v>2026-06-15</v>
       </c>
       <c r="M122" t="str">
-        <v>인접 호수와 함께 벽체구분 없이 이용중이며, 현재는 공실임.</v>
-      </c>
-    </row>
-    <row r="123" xml:space="preserve">
+        <v>공부상 판매영업시설(상점)이나, 현황 벽체가 없고 인접호수와 경계가 구분되지 않는 오픈형상가로 현황 의류매장으로 이용중임.</v>
+      </c>
+    </row>
+    <row r="123">
       <c r="A123" t="str">
-        <v>성남 수정구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B123" t="str">
         <v>성남지원</v>
       </c>
       <c r="C123" t="str">
-        <v>성남지원 2024타경7156</v>
+        <v>성남지원 2025타경2295</v>
       </c>
       <c r="D123" t="str">
         <v>1</v>
       </c>
       <c r="E123" t="str">
-        <v>경기도 성남시 수정구 고등동 527-54</v>
+        <v>경기도 성남시 중원구 성남동 2164 영건센스빌오피스텔 3층 301호</v>
       </c>
       <c r="F123">
-        <v>662</v>
+        <v>122.42</v>
       </c>
       <c r="G123">
-        <v>200.3</v>
+        <v>37</v>
       </c>
       <c r="H123">
-        <v>43423440</v>
+        <v>1365000000</v>
       </c>
       <c r="I123">
-        <v>7298000</v>
+        <v>955500000</v>
       </c>
       <c r="J123">
-        <v>16.8</v>
+        <v>70</v>
       </c>
       <c r="K123" t="str">
-        <v>유찰 5회</v>
+        <v>유찰 2회</v>
       </c>
       <c r="L123" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M123" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 공유자의 우선매수신고는 1회에 한하여 행사할 수 있음(공유자가 우선매수권 신고 후 매각기일까지 매수보증금을 미납하여 실효되는 경우에는 그 공유자는 이후 매각기일부터는 우선매수권을 행사할 수 없음).
-2. 재매각, 매수보증금은 최저매각가격의 20%임.</v>
+      <c r="M123" t="str">
+        <v>일괄매각, 목록1,2는 벽체를 제거한 후 구분없이 사용 중.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>성남 분당구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B124" t="str">
         <v>성남지원</v>
       </c>
       <c r="C124" t="str">
-        <v>성남지원 2024타경66599</v>
+        <v>성남지원 2025타경2295</v>
       </c>
       <c r="D124" t="str">
         <v>1</v>
       </c>
       <c r="E124" t="str">
-        <v>경기도 성남시 분당구 성남대로925번길 16 (야탑동,성남(분당)여객자동차터미널및복합건물) 3층103호</v>
+        <v>경기도 성남시 중원구 성남동 2164 영건센스빌오피스텔 3층 302호</v>
       </c>
       <c r="F124">
-        <v>49.83</v>
+        <v>68.79</v>
       </c>
       <c r="G124">
-        <v>15.1</v>
+        <v>20.8</v>
       </c>
       <c r="H124">
-        <v>739000000</v>
+        <v>1365000000</v>
       </c>
       <c r="I124">
-        <v>177434000</v>
+        <v>955500000</v>
       </c>
       <c r="J124">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="K124" t="str">
-        <v>유찰 5회</v>
+        <v>유찰 2회</v>
       </c>
       <c r="L124" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M124" t="str">
-        <v/>
+        <v>일괄매각, 목록1,2는 벽체를 제거한 후 구분없이 사용 중.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>성남 분당구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B125" t="str">
         <v>성남지원</v>
       </c>
       <c r="C125" t="str">
-        <v>성남지원 2024타경67486</v>
+        <v>성남지원 2025타경2295</v>
       </c>
       <c r="D125" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="str">
-        <v>경기도 성남시 분당구 성남대로925번길 16</v>
+        <v>경기도 성남시 중원구 성남동 2164 영건센스빌오피스텔 12층 1201호</v>
       </c>
       <c r="F125">
-        <v>48.26</v>
+        <v>127.58</v>
       </c>
       <c r="G125">
-        <v>14.6</v>
+        <v>38.6</v>
       </c>
       <c r="H125">
-        <v>611000000</v>
+        <v>400000000</v>
       </c>
       <c r="I125">
-        <v>209573000</v>
+        <v>280000000</v>
       </c>
       <c r="J125">
-        <v>34.3</v>
+        <v>70</v>
       </c>
       <c r="K125" t="str">
-        <v>유찰 4회</v>
+        <v>유찰 2회</v>
       </c>
       <c r="L125" t="str">
         <v>2026-06-15</v>
@@ -5577,37 +5570,37 @@
         <v>성남지원</v>
       </c>
       <c r="C126" t="str">
-        <v>성남지원 2025타경442</v>
+        <v>성남지원 2025타경3472</v>
       </c>
       <c r="D126" t="str">
         <v>1</v>
       </c>
       <c r="E126" t="str">
-        <v>경기도 성남시 중원구 도촌동 산9</v>
+        <v>경기도 성남시 중원구 상대원동 333-7 금강펜테리움아이티타워 3층에이-302호</v>
       </c>
       <c r="F126">
-        <v>11901</v>
+        <v>169.77</v>
       </c>
       <c r="G126">
-        <v>3600.1</v>
+        <v>51.4</v>
       </c>
       <c r="H126">
-        <v>1713744000</v>
+        <v>610000000</v>
       </c>
       <c r="I126">
-        <v>411471000</v>
+        <v>427000000</v>
       </c>
       <c r="J126">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="K126" t="str">
-        <v>유찰 5회</v>
+        <v>유찰 2회</v>
       </c>
       <c r="L126" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M126" t="str">
-        <v/>
+        <v>아파트형공장으로 이용중임.</v>
       </c>
     </row>
     <row r="127">
@@ -5618,119 +5611,120 @@
         <v>성남지원</v>
       </c>
       <c r="C127" t="str">
-        <v>성남지원 2025타경503</v>
+        <v>성남지원 2025타경3540</v>
       </c>
       <c r="D127" t="str">
         <v>1</v>
       </c>
       <c r="E127" t="str">
-        <v>경기도 성남시 분당구 서현동 275 라포르테블랑서현 605호</v>
+        <v>경기도 성남시 분당구 삼평동 713 천석미래로주건축물제1동 3층313호</v>
       </c>
       <c r="F127">
-        <v>28.5058</v>
+        <v>35.24</v>
       </c>
       <c r="G127">
-        <v>8.6</v>
+        <v>10.7</v>
       </c>
       <c r="H127">
-        <v>1245900000</v>
+        <v>315000000</v>
       </c>
       <c r="I127">
-        <v>610491000</v>
+        <v>315000000</v>
       </c>
       <c r="J127">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="K127" t="str">
-        <v>유찰 3회</v>
+        <v>신건</v>
       </c>
       <c r="L127" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M127" t="str">
-        <v>일괄매각</v>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>성남 분당구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B128" t="str">
         <v>성남지원</v>
       </c>
       <c r="C128" t="str">
-        <v>성남지원 2025타경503</v>
+        <v>성남지원 2025타경4444</v>
       </c>
       <c r="D128" t="str">
         <v>1</v>
       </c>
       <c r="E128" t="str">
-        <v>경기도 성남시 분당구 서현동 275 라포르테블랑서현 제1주차장호</v>
+        <v>경기도 성남시 중원구 하대원동 115-3 성원초원아파트 102동 5층508호</v>
       </c>
       <c r="F128">
-        <v>3197.0632</v>
+        <v>84.975</v>
       </c>
       <c r="G128">
-        <v>967.1</v>
+        <v>25.7</v>
       </c>
       <c r="H128">
-        <v>1245900000</v>
+        <v>203000000</v>
       </c>
       <c r="I128">
-        <v>610491000</v>
+        <v>203000000</v>
       </c>
       <c r="J128">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="K128" t="str">
-        <v>유찰 3회</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L128" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M128" t="str">
-        <v>일괄매각</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>공유자의 우선매수신고는 1회에 한하여 행사할 수 있음(공유자가 우선매수권 신고 후 매각기일까지 매수보증금을 미납하여 실효되는 경우에는 그 공유자는 이후 매각기일부터는 우선매수권을 행사할 수 없음).</v>
+      </c>
+    </row>
+    <row r="129" xml:space="preserve">
       <c r="A129" t="str">
-        <v>성남 수정구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B129" t="str">
         <v>성남지원</v>
       </c>
       <c r="C129" t="str">
-        <v>성남지원 2025타경930</v>
+        <v>성남지원 2025타경51998</v>
       </c>
       <c r="D129" t="str">
         <v>1</v>
       </c>
       <c r="E129" t="str">
-        <v>경기도 성남시 수정구 사송동 산89</v>
+        <v>경기도 성남시 중원구 도촌동 562 으뜸이레가 4층403호</v>
       </c>
       <c r="F129">
-        <v>1915</v>
+        <v>37.527</v>
       </c>
       <c r="G129">
-        <v>579.3</v>
+        <v>11.4</v>
       </c>
       <c r="H129">
-        <v>1419015000</v>
+        <v>223000000</v>
       </c>
       <c r="I129">
-        <v>340706000</v>
+        <v>223000000</v>
       </c>
       <c r="J129">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="K129" t="str">
-        <v>유찰 5회</v>
+        <v>신건</v>
       </c>
       <c r="L129" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M129" t="str">
-        <v>지적도상 지목 도로와 접했으나. 현황은 자연림,맹지임.</v>
+      <c r="M129" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 공부상 업무시설(오피스텔)이나 현황 주거용 오피스텔로 이용중임.
+2. 전세사기피해자특별법 제20조에 의한전세사기피해자는 우선매수권행사를 할수 있음(단, 우선매수권행사는 1회에 한함)</v>
       </c>
     </row>
     <row r="130">
@@ -5741,66 +5735,66 @@
         <v>성남지원</v>
       </c>
       <c r="C130" t="str">
-        <v>성남지원 2025타경2226</v>
+        <v>성남지원 2025타경52052</v>
       </c>
       <c r="D130" t="str">
         <v>1</v>
       </c>
       <c r="E130" t="str">
-        <v>경기도 성남시 중원구 성남동 3499 니즈몰 1층1011호</v>
+        <v>경기도 성남시 중원구 도촌동 562 으뜸이레가 5층 507호</v>
       </c>
       <c r="F130">
-        <v>3.74</v>
+        <v>48.331</v>
       </c>
       <c r="G130">
-        <v>1.1</v>
+        <v>14.6</v>
       </c>
       <c r="H130">
-        <v>47000000</v>
+        <v>276000000</v>
       </c>
       <c r="I130">
-        <v>32900000</v>
+        <v>94668000</v>
       </c>
       <c r="J130">
-        <v>70</v>
+        <v>34.3</v>
       </c>
       <c r="K130" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 4회</v>
       </c>
       <c r="L130" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M130" t="str">
-        <v>공부상 판매영업시설(상점)이나, 현황 벽체가 없고 인접호수와 경계가 구분되지 않는 오픈형상가로 현황 의류매장으로 이용중임.</v>
+        <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>성남 중원구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B131" t="str">
         <v>성남지원</v>
       </c>
       <c r="C131" t="str">
-        <v>성남지원 2025타경2295</v>
+        <v>성남지원 2025타경52423</v>
       </c>
       <c r="D131" t="str">
         <v>1</v>
       </c>
       <c r="E131" t="str">
-        <v>경기도 성남시 중원구 성남동 2164 영건센스빌오피스텔 3층 301호</v>
+        <v>경기도 성남시 수정구 양지동 484 1층 102호</v>
       </c>
       <c r="F131">
-        <v>122.42</v>
+        <v>41.22</v>
       </c>
       <c r="G131">
-        <v>37</v>
+        <v>12.5</v>
       </c>
       <c r="H131">
-        <v>1365000000</v>
+        <v>285000000</v>
       </c>
       <c r="I131">
-        <v>955500000</v>
+        <v>199500000</v>
       </c>
       <c r="J131">
         <v>70</v>
@@ -5812,36 +5806,36 @@
         <v>2026-06-15</v>
       </c>
       <c r="M131" t="str">
-        <v>일괄매각, 목록1,2는 벽체를 제거한 후 구분없이 사용 중.</v>
+        <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B132" t="str">
         <v>성남지원</v>
       </c>
       <c r="C132" t="str">
-        <v>성남지원 2025타경2295</v>
+        <v>성남지원 2025타경52448</v>
       </c>
       <c r="D132" t="str">
         <v>1</v>
       </c>
       <c r="E132" t="str">
-        <v>경기도 성남시 중원구 성남동 2164 영건센스빌오피스텔 3층 302호</v>
+        <v>경기도 성남시 분당구 대장동 616-1 클라우드베이6 1층 115호</v>
       </c>
       <c r="F132">
-        <v>68.79</v>
+        <v>44.15</v>
       </c>
       <c r="G132">
-        <v>20.8</v>
+        <v>13.4</v>
       </c>
       <c r="H132">
-        <v>1365000000</v>
+        <v>1072000000</v>
       </c>
       <c r="I132">
-        <v>955500000</v>
+        <v>750400000</v>
       </c>
       <c r="J132">
         <v>70</v>
@@ -5853,159 +5847,159 @@
         <v>2026-06-15</v>
       </c>
       <c r="M132" t="str">
-        <v>일괄매각, 목록1,2는 벽체를 제거한 후 구분없이 사용 중.</v>
+        <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>성남 중원구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B133" t="str">
         <v>성남지원</v>
       </c>
       <c r="C133" t="str">
-        <v>성남지원 2025타경2295</v>
+        <v>성남지원 2025타경52574</v>
       </c>
       <c r="D133" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133" t="str">
-        <v>경기도 성남시 중원구 성남동 2164 영건센스빌오피스텔 12층 1201호</v>
+        <v>경기도 성남시 수정구 상적동 316-4</v>
       </c>
       <c r="F133">
-        <v>127.58</v>
+        <v>61.44</v>
       </c>
       <c r="G133">
-        <v>38.6</v>
+        <v>18.6</v>
       </c>
       <c r="H133">
-        <v>400000000</v>
+        <v>1175922800</v>
       </c>
       <c r="I133">
-        <v>280000000</v>
+        <v>1175922800</v>
       </c>
       <c r="J133">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K133" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L133" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>일괄매각. 제시외 건물 포함</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>성남 중원구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B134" t="str">
         <v>성남지원</v>
       </c>
       <c r="C134" t="str">
-        <v>성남지원 2025타경3472</v>
+        <v>성남지원 2025타경52574</v>
       </c>
       <c r="D134" t="str">
         <v>1</v>
       </c>
       <c r="E134" t="str">
-        <v>경기도 성남시 중원구 상대원동 333-7 금강펜테리움아이티타워 3층에이-302호</v>
+        <v>경기도 성남시 수정구 상적동 316-4</v>
       </c>
       <c r="F134">
-        <v>169.77</v>
+        <v>235</v>
       </c>
       <c r="G134">
-        <v>51.4</v>
+        <v>71.1</v>
       </c>
       <c r="H134">
-        <v>610000000</v>
+        <v>1175922800</v>
       </c>
       <c r="I134">
-        <v>427000000</v>
+        <v>1175922800</v>
       </c>
       <c r="J134">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K134" t="str">
-        <v>유찰 2회</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L134" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M134" t="str">
-        <v>아파트형공장으로 이용중임.</v>
+        <v>일괄매각. 제시외 건물 포함</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>성남 분당구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B135" t="str">
         <v>성남지원</v>
       </c>
       <c r="C135" t="str">
-        <v>성남지원 2025타경3540</v>
+        <v>성남지원 2025타경52591</v>
       </c>
       <c r="D135" t="str">
         <v>1</v>
       </c>
       <c r="E135" t="str">
-        <v>경기도 성남시 분당구 삼평동 713 천석미래로주건축물제1동 3층313호</v>
+        <v>경기도 성남시 중원구 도촌동 562 으뜸이레가 4층401호</v>
       </c>
       <c r="F135">
-        <v>35.24</v>
+        <v>28.187</v>
       </c>
       <c r="G135">
-        <v>10.7</v>
+        <v>8.5</v>
       </c>
       <c r="H135">
-        <v>315000000</v>
+        <v>155000000</v>
       </c>
       <c r="I135">
-        <v>315000000</v>
+        <v>108500000</v>
       </c>
       <c r="J135">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K135" t="str">
-        <v>신건</v>
+        <v>유찰 2회</v>
       </c>
       <c r="L135" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>주거용 오피스텔로 이용중임.</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B136" t="str">
         <v>성남지원</v>
       </c>
       <c r="C136" t="str">
-        <v>성남지원 2025타경4444</v>
+        <v>성남지원 2025타경52714</v>
       </c>
       <c r="D136" t="str">
         <v>1</v>
       </c>
       <c r="E136" t="str">
-        <v>경기도 성남시 중원구 하대원동 115-3 성원초원아파트 102동 5층508호</v>
+        <v>경기도 성남시 분당구 백현동 540 힐스테이트판교역(7-1블럭)판매시설 지2층비2009호</v>
       </c>
       <c r="F136">
-        <v>84.975</v>
+        <v>26.69</v>
       </c>
       <c r="G136">
-        <v>25.7</v>
+        <v>8.1</v>
       </c>
       <c r="H136">
-        <v>203000000</v>
+        <v>829000000</v>
       </c>
       <c r="I136">
-        <v>203000000</v>
+        <v>829000000</v>
       </c>
       <c r="J136">
         <v>100</v>
@@ -6017,10 +6011,10 @@
         <v>2026-06-15</v>
       </c>
       <c r="M136" t="str">
-        <v>공유자의 우선매수신고는 1회에 한하여 행사할 수 있음(공유자가 우선매수권 신고 후 매각기일까지 매수보증금을 미납하여 실효되는 경우에는 그 공유자는 이후 매각기일부터는 우선매수권을 행사할 수 없음).</v>
-      </c>
-    </row>
-    <row r="137" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
       <c r="A137" t="str">
         <v>성남 중원구</v>
       </c>
@@ -6028,38 +6022,37 @@
         <v>성남지원</v>
       </c>
       <c r="C137" t="str">
-        <v>성남지원 2025타경51998</v>
+        <v>성남지원 2025타경52805</v>
       </c>
       <c r="D137" t="str">
         <v>1</v>
       </c>
       <c r="E137" t="str">
-        <v>경기도 성남시 중원구 도촌동 562 으뜸이레가 4층403호</v>
+        <v>경기도 성남시 중원구 하대원동 111-40</v>
       </c>
       <c r="F137">
-        <v>37.527</v>
+        <v>115.9</v>
       </c>
       <c r="G137">
-        <v>11.4</v>
+        <v>35.1</v>
       </c>
       <c r="H137">
-        <v>223000000</v>
+        <v>749239600</v>
       </c>
       <c r="I137">
-        <v>223000000</v>
+        <v>749239600</v>
       </c>
       <c r="J137">
         <v>100</v>
       </c>
       <c r="K137" t="str">
-        <v>신건</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L137" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M137" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 공부상 업무시설(오피스텔)이나 현황 주거용 오피스텔로 이용중임.
-2. 전세사기피해자특별법 제20조에 의한전세사기피해자는 우선매수권행사를 할수 있음(단, 우선매수권행사는 1회에 한함)</v>
+      <c r="M137" t="str">
+        <v>일괄매각. 제시외 샷시조 샷시지붕 포함</v>
       </c>
     </row>
     <row r="138">
@@ -6070,66 +6063,66 @@
         <v>성남지원</v>
       </c>
       <c r="C138" t="str">
-        <v>성남지원 2025타경52052</v>
+        <v>성남지원 2025타경52805</v>
       </c>
       <c r="D138" t="str">
         <v>1</v>
       </c>
       <c r="E138" t="str">
-        <v>경기도 성남시 중원구 도촌동 562 으뜸이레가 5층 507호</v>
+        <v>경기도 성남시 중원구 하대원동 111-40</v>
       </c>
       <c r="F138">
-        <v>48.331</v>
+        <v>69.24</v>
       </c>
       <c r="G138">
-        <v>14.6</v>
+        <v>20.9</v>
       </c>
       <c r="H138">
-        <v>276000000</v>
+        <v>749239600</v>
       </c>
       <c r="I138">
-        <v>94668000</v>
+        <v>749239600</v>
       </c>
       <c r="J138">
-        <v>34.3</v>
+        <v>100</v>
       </c>
       <c r="K138" t="str">
-        <v>유찰 4회</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L138" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>일괄매각. 제시외 샷시조 샷시지붕 포함</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>성남 수정구</v>
+        <v>성남 중원구</v>
       </c>
       <c r="B139" t="str">
         <v>성남지원</v>
       </c>
       <c r="C139" t="str">
-        <v>성남지원 2025타경52423</v>
+        <v>성남지원 2025타경52903</v>
       </c>
       <c r="D139" t="str">
         <v>1</v>
       </c>
       <c r="E139" t="str">
-        <v>경기도 성남시 수정구 양지동 484 1층 102호</v>
+        <v>경기도 성남시 중원구 성남동 3135 지앤느모란 4층408호</v>
       </c>
       <c r="F139">
-        <v>41.22</v>
+        <v>21.42</v>
       </c>
       <c r="G139">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="H139">
-        <v>285000000</v>
+        <v>158000000</v>
       </c>
       <c r="I139">
-        <v>199500000</v>
+        <v>110600000</v>
       </c>
       <c r="J139">
         <v>70</v>
@@ -6141,7 +6134,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="M139" t="str">
-        <v/>
+        <v>오피스텔로 이용중임.</v>
       </c>
     </row>
     <row r="140">
@@ -6152,31 +6145,31 @@
         <v>성남지원</v>
       </c>
       <c r="C140" t="str">
-        <v>성남지원 2025타경52448</v>
+        <v>성남지원 2025타경52912</v>
       </c>
       <c r="D140" t="str">
         <v>1</v>
       </c>
       <c r="E140" t="str">
-        <v>경기도 성남시 분당구 대장동 616-1 클라우드베이6 1층 115호</v>
+        <v>경기도 성남시 분당구 수내동 79-2 5층1호</v>
       </c>
       <c r="F140">
-        <v>44.15</v>
+        <v>926.37</v>
       </c>
       <c r="G140">
-        <v>13.4</v>
+        <v>280.2</v>
       </c>
       <c r="H140">
-        <v>1072000000</v>
+        <v>3200000000</v>
       </c>
       <c r="I140">
-        <v>750400000</v>
+        <v>3200000000</v>
       </c>
       <c r="J140">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K140" t="str">
-        <v>유찰 2회</v>
+        <v>신건</v>
       </c>
       <c r="L140" t="str">
         <v>2026-06-15</v>
@@ -6193,107 +6186,107 @@
         <v>성남지원</v>
       </c>
       <c r="C141" t="str">
-        <v>성남지원 2025타경52574</v>
+        <v>성남지원 2025타경52980</v>
       </c>
       <c r="D141" t="str">
         <v>1</v>
       </c>
       <c r="E141" t="str">
-        <v>경기도 성남시 수정구 상적동 316-4</v>
+        <v>경기도 성남시 수정구 단대동 46-6 지하층1호</v>
       </c>
       <c r="F141">
-        <v>61.44</v>
+        <v>43.07</v>
       </c>
       <c r="G141">
-        <v>18.6</v>
+        <v>13</v>
       </c>
       <c r="H141">
-        <v>1175922800</v>
+        <v>167000000</v>
       </c>
       <c r="I141">
-        <v>1175922800</v>
+        <v>167000000</v>
       </c>
       <c r="J141">
         <v>100</v>
       </c>
       <c r="K141" t="str">
-        <v>유찰 1회</v>
+        <v>신건</v>
       </c>
       <c r="L141" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M141" t="str">
-        <v>일괄매각. 제시외 건물 포함</v>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>성남 수정구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B142" t="str">
         <v>성남지원</v>
       </c>
       <c r="C142" t="str">
-        <v>성남지원 2025타경52574</v>
+        <v>성남지원 2025타경53037</v>
       </c>
       <c r="D142" t="str">
         <v>1</v>
       </c>
       <c r="E142" t="str">
-        <v>경기도 성남시 수정구 상적동 316-4</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제1층 제148호</v>
       </c>
       <c r="F142">
-        <v>235</v>
+        <v>6.04</v>
       </c>
       <c r="G142">
-        <v>71.1</v>
+        <v>1.8</v>
       </c>
       <c r="H142">
-        <v>1175922800</v>
+        <v>35000000</v>
       </c>
       <c r="I142">
-        <v>1175922800</v>
+        <v>35000000</v>
       </c>
       <c r="J142">
         <v>100</v>
       </c>
       <c r="K142" t="str">
-        <v>유찰 1회</v>
+        <v>신건</v>
       </c>
       <c r="L142" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M142" t="str">
-        <v>일괄매각. 제시외 건물 포함</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>인근 다수 물건 및 공용부분과 함께 벽체없이 이용중이며 현재는 공실임.</v>
+      </c>
+    </row>
+    <row r="143" xml:space="preserve">
       <c r="A143" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B143" t="str">
         <v>성남지원</v>
       </c>
       <c r="C143" t="str">
-        <v>성남지원 2025타경52591</v>
+        <v>성남지원 2025타경53063</v>
       </c>
       <c r="D143" t="str">
         <v>1</v>
       </c>
       <c r="E143" t="str">
-        <v>경기도 성남시 중원구 도촌동 562 으뜸이레가 4층401호</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 제713호</v>
       </c>
       <c r="F143">
-        <v>28.187</v>
+        <v>4.8</v>
       </c>
       <c r="G143">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="H143">
-        <v>155000000</v>
+        <v>26000000</v>
       </c>
       <c r="I143">
-        <v>108500000</v>
+        <v>18200000</v>
       </c>
       <c r="J143">
         <v>70</v>
@@ -6304,8 +6297,9 @@
       <c r="L143" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M143" t="str">
-        <v>주거용 오피스텔로 이용중임.</v>
+      <c r="M143" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 판매 및 영업시설로 벽체구분없는 오픈형 상가로 현재 공실상태임.
+2. 집합건축물대장(표제부,갑)상 위반건축물로 등재되어 있으므로 개별확인요망.</v>
       </c>
     </row>
     <row r="144">
@@ -6316,66 +6310,66 @@
         <v>성남지원</v>
       </c>
       <c r="C144" t="str">
-        <v>성남지원 2025타경52714</v>
+        <v>성남지원 2025타경53148</v>
       </c>
       <c r="D144" t="str">
         <v>1</v>
       </c>
       <c r="E144" t="str">
-        <v>경기도 성남시 분당구 백현동 540 힐스테이트판교역(7-1블럭)판매시설 지2층비2009호</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 311호</v>
       </c>
       <c r="F144">
-        <v>26.69</v>
+        <v>6.98</v>
       </c>
       <c r="G144">
-        <v>8.1</v>
+        <v>2.1</v>
       </c>
       <c r="H144">
-        <v>829000000</v>
+        <v>50000000</v>
       </c>
       <c r="I144">
-        <v>829000000</v>
+        <v>35000000</v>
       </c>
       <c r="J144">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="K144" t="str">
-        <v>유찰 1회</v>
+        <v>유찰 2회</v>
       </c>
       <c r="L144" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M144" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="145">
+        <v>판매 및 영업시설이며 현재 공실상태임.</v>
+      </c>
+    </row>
+    <row r="145" xml:space="preserve">
       <c r="A145" t="str">
-        <v>성남 중원구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B145" t="str">
         <v>성남지원</v>
       </c>
       <c r="C145" t="str">
-        <v>성남지원 2025타경52805</v>
+        <v>성남지원 2025타경53159</v>
       </c>
       <c r="D145" t="str">
         <v>1</v>
       </c>
       <c r="E145" t="str">
-        <v>경기도 성남시 중원구 하대원동 111-40</v>
+        <v>경기도 성남시 수정구 양지동 749</v>
       </c>
       <c r="F145">
-        <v>115.9</v>
+        <v>165.4</v>
       </c>
       <c r="G145">
-        <v>35.1</v>
+        <v>50</v>
       </c>
       <c r="H145">
-        <v>749239600</v>
+        <v>1079351350</v>
       </c>
       <c r="I145">
-        <v>749239600</v>
+        <v>1079351350</v>
       </c>
       <c r="J145">
         <v>100</v>
@@ -6386,37 +6380,39 @@
       <c r="L145" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M145" t="str">
-        <v>일괄매각. 제시외 샷시조 샷시지붕 포함</v>
-      </c>
-    </row>
-    <row r="146">
+      <c r="M145" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 일괄매각.  
+2. 건물 1층은 공부상 "연탄창고"로 기재되어 있으나 현황 주택으로 이용중임.
+3. 건물등기사항증명서 및 일반건축물대장에 부속건물인 단층 화장실이 기재되어 있으나 현황 소재불명으로 평가 및 매각에서 제외하고, 옥탑소재 제시외 건물(샷시조 함석지붕 계단실 약2㎡)도 평가 및 매각에서 제외함.</v>
+      </c>
+    </row>
+    <row r="146" xml:space="preserve">
       <c r="A146" t="str">
-        <v>성남 중원구</v>
+        <v>성남 수정구</v>
       </c>
       <c r="B146" t="str">
         <v>성남지원</v>
       </c>
       <c r="C146" t="str">
-        <v>성남지원 2025타경52805</v>
+        <v>성남지원 2025타경53159</v>
       </c>
       <c r="D146" t="str">
         <v>1</v>
       </c>
       <c r="E146" t="str">
-        <v>경기도 성남시 중원구 하대원동 111-40</v>
+        <v>경기도 성남시 수정구 양지동 749</v>
       </c>
       <c r="F146">
-        <v>69.24</v>
+        <v>38.23</v>
       </c>
       <c r="G146">
-        <v>20.9</v>
+        <v>11.6</v>
       </c>
       <c r="H146">
-        <v>749239600</v>
+        <v>1079351350</v>
       </c>
       <c r="I146">
-        <v>749239600</v>
+        <v>1079351350</v>
       </c>
       <c r="J146">
         <v>100</v>
@@ -6427,49 +6423,51 @@
       <c r="L146" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M146" t="str">
-        <v>일괄매각. 제시외 샷시조 샷시지붕 포함</v>
+      <c r="M146" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 일괄매각.  
+2. 건물 1층은 공부상 "연탄창고"로 기재되어 있으나 현황 주택으로 이용중임.
+3. 건물등기사항증명서 및 일반건축물대장에 부속건물인 단층 화장실이 기재되어 있으나 현황 소재불명으로 평가 및 매각에서 제외하고, 옥탑소재 제시외 건물(샷시조 함석지붕 계단실 약2㎡)도 평가 및 매각에서 제외함.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>성남 중원구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B147" t="str">
         <v>성남지원</v>
       </c>
       <c r="C147" t="str">
-        <v>성남지원 2025타경52903</v>
+        <v>성남지원 2025타경53173</v>
       </c>
       <c r="D147" t="str">
         <v>1</v>
       </c>
       <c r="E147" t="str">
-        <v>경기도 성남시 중원구 성남동 3135 지앤느모란 4층408호</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 지2층407호</v>
       </c>
       <c r="F147">
-        <v>21.42</v>
+        <v>8.23</v>
       </c>
       <c r="G147">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="H147">
-        <v>158000000</v>
+        <v>75000000</v>
       </c>
       <c r="I147">
-        <v>110600000</v>
+        <v>75000000</v>
       </c>
       <c r="J147">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K147" t="str">
-        <v>유찰 2회</v>
+        <v>신건</v>
       </c>
       <c r="L147" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M147" t="str">
-        <v>오피스텔로 이용중임.</v>
+        <v>판매 및 영업시설로 이용중이며 벽체구분없는 오픈형 상가로 현재 공실상태임.</v>
       </c>
     </row>
     <row r="148">
@@ -6480,37 +6478,37 @@
         <v>성남지원</v>
       </c>
       <c r="C148" t="str">
-        <v>성남지원 2025타경52912</v>
+        <v>성남지원 2025타경53329</v>
       </c>
       <c r="D148" t="str">
         <v>1</v>
       </c>
       <c r="E148" t="str">
-        <v>경기도 성남시 분당구 수내동 79-2 5층1호</v>
+        <v>경기도 성남시 분당구 구미동 159 월드쇼핑(씨지브이 스퀘어) 1층시-153호</v>
       </c>
       <c r="F148">
-        <v>926.37</v>
+        <v>8.96</v>
       </c>
       <c r="G148">
-        <v>280.2</v>
+        <v>2.7</v>
       </c>
       <c r="H148">
-        <v>3200000000</v>
+        <v>62000000</v>
       </c>
       <c r="I148">
-        <v>3200000000</v>
+        <v>62000000</v>
       </c>
       <c r="J148">
         <v>100</v>
       </c>
       <c r="K148" t="str">
-        <v>신건</v>
+        <v>유찰 1회</v>
       </c>
       <c r="L148" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M148" t="str">
-        <v/>
+        <v>본건 건물은 오픈형 상가로 벽체 구분없이 인접호수와 일체로 판매 및 영업시설(카페포토)로 이용중임.</v>
       </c>
     </row>
     <row r="149">
@@ -6521,25 +6519,25 @@
         <v>성남지원</v>
       </c>
       <c r="C149" t="str">
-        <v>성남지원 2025타경52980</v>
+        <v>성남지원 2025타경53512</v>
       </c>
       <c r="D149" t="str">
         <v>1</v>
       </c>
       <c r="E149" t="str">
-        <v>경기도 성남시 수정구 단대동 46-6 지하층1호</v>
+        <v>경기도 성남시 수정구 창곡동 559-6 라크리움 2층209호</v>
       </c>
       <c r="F149">
-        <v>43.07</v>
+        <v>73.5</v>
       </c>
       <c r="G149">
-        <v>13</v>
+        <v>22.2</v>
       </c>
       <c r="H149">
-        <v>167000000</v>
+        <v>561000000</v>
       </c>
       <c r="I149">
-        <v>167000000</v>
+        <v>561000000</v>
       </c>
       <c r="J149">
         <v>100</v>
@@ -6551,7 +6549,7 @@
         <v>2026-06-15</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>건축물대장상 제2종근린생활시설(학원)으로 이용중이며, 현재 공실상태임.</v>
       </c>
     </row>
     <row r="150">
@@ -6562,25 +6560,25 @@
         <v>성남지원</v>
       </c>
       <c r="C150" t="str">
-        <v>성남지원 2025타경53037</v>
+        <v>성남지원 2025타경53550</v>
       </c>
       <c r="D150" t="str">
         <v>1</v>
       </c>
       <c r="E150" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제1층 제148호</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제2층 제205호</v>
       </c>
       <c r="F150">
-        <v>6.04</v>
+        <v>6.29</v>
       </c>
       <c r="G150">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H150">
-        <v>35000000</v>
+        <v>26200000</v>
       </c>
       <c r="I150">
-        <v>35000000</v>
+        <v>26200000</v>
       </c>
       <c r="J150">
         <v>100</v>
@@ -6592,10 +6590,10 @@
         <v>2026-06-15</v>
       </c>
       <c r="M150" t="str">
-        <v>인근 다수 물건 및 공용부분과 함께 벽체없이 이용중이며 현재는 공실임.</v>
-      </c>
-    </row>
-    <row r="151" xml:space="preserve">
+        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가로 현재 공실상태임.</v>
+      </c>
+    </row>
+    <row r="151">
       <c r="A151" t="str">
         <v>성남 분당구</v>
       </c>
@@ -6603,38 +6601,37 @@
         <v>성남지원</v>
       </c>
       <c r="C151" t="str">
-        <v>성남지원 2025타경53063</v>
+        <v>성남지원 2025타경53676</v>
       </c>
       <c r="D151" t="str">
         <v>1</v>
       </c>
       <c r="E151" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 제713호</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 제248호</v>
       </c>
       <c r="F151">
-        <v>4.8</v>
+        <v>6.99</v>
       </c>
       <c r="G151">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="H151">
-        <v>26000000</v>
+        <v>48000000</v>
       </c>
       <c r="I151">
-        <v>18200000</v>
+        <v>48000000</v>
       </c>
       <c r="J151">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K151" t="str">
-        <v>유찰 2회</v>
+        <v>신건</v>
       </c>
       <c r="L151" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M151" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 판매 및 영업시설로 벽체구분없는 오픈형 상가로 현재 공실상태임.
-2. 집합건축물대장(표제부,갑)상 위반건축물로 등재되어 있으므로 개별확인요망.</v>
+      <c r="M151" t="str">
+        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가임.</v>
       </c>
     </row>
     <row r="152">
@@ -6645,458 +6642,126 @@
         <v>성남지원</v>
       </c>
       <c r="C152" t="str">
-        <v>성남지원 2025타경53148</v>
+        <v>성남지원 2025타경53690</v>
       </c>
       <c r="D152" t="str">
         <v>1</v>
       </c>
       <c r="E152" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 311호</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 제340호</v>
       </c>
       <c r="F152">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
       <c r="G152">
         <v>2.1</v>
       </c>
       <c r="H152">
-        <v>50000000</v>
+        <v>51840000</v>
       </c>
       <c r="I152">
-        <v>35000000</v>
+        <v>51840000</v>
       </c>
       <c r="J152">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K152" t="str">
-        <v>유찰 2회</v>
+        <v>신건</v>
       </c>
       <c r="L152" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M152" t="str">
-        <v>판매 및 영업시설이며 현재 공실상태임.</v>
-      </c>
-    </row>
-    <row r="153" xml:space="preserve">
+        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가로 현재 공실상태임.</v>
+      </c>
+    </row>
+    <row r="153">
       <c r="A153" t="str">
-        <v>성남 수정구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B153" t="str">
         <v>성남지원</v>
       </c>
       <c r="C153" t="str">
-        <v>성남지원 2025타경53159</v>
+        <v>성남지원 2025타경53768</v>
       </c>
       <c r="D153" t="str">
         <v>1</v>
       </c>
       <c r="E153" t="str">
-        <v>경기도 성남시 수정구 양지동 749</v>
+        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제1층 제123호</v>
       </c>
       <c r="F153">
-        <v>165.4</v>
+        <v>5.28</v>
       </c>
       <c r="G153">
-        <v>50</v>
+        <v>1.6</v>
       </c>
       <c r="H153">
-        <v>1079351350</v>
+        <v>47000000</v>
       </c>
       <c r="I153">
-        <v>1079351350</v>
+        <v>47000000</v>
       </c>
       <c r="J153">
         <v>100</v>
       </c>
       <c r="K153" t="str">
-        <v>유찰 1회</v>
+        <v>신건</v>
       </c>
       <c r="L153" t="str">
         <v>2026-06-15</v>
       </c>
-      <c r="M153" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 일괄매각.  
-2. 건물 1층은 공부상 "연탄창고"로 기재되어 있으나 현황 주택으로 이용중임.
-3. 건물등기사항증명서 및 일반건축물대장에 부속건물인 단층 화장실이 기재되어 있으나 현황 소재불명으로 평가 및 매각에서 제외하고, 옥탑소재 제시외 건물(샷시조 함석지붕 계단실 약2㎡)도 평가 및 매각에서 제외함.</v>
+      <c r="M153" t="str">
+        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가임.</v>
       </c>
     </row>
     <row r="154" xml:space="preserve">
       <c r="A154" t="str">
-        <v>성남 수정구</v>
+        <v>성남 분당구</v>
       </c>
       <c r="B154" t="str">
         <v>성남지원</v>
       </c>
       <c r="C154" t="str">
-        <v>성남지원 2025타경53159</v>
+        <v>성남지원 2025타경53798</v>
       </c>
       <c r="D154" t="str">
         <v>1</v>
       </c>
       <c r="E154" t="str">
-        <v>경기도 성남시 수정구 양지동 749</v>
+        <v>경기도 성남시 분당구 서현동 183</v>
       </c>
       <c r="F154">
-        <v>38.23</v>
+        <v>655</v>
       </c>
       <c r="G154">
-        <v>11.6</v>
+        <v>198.1</v>
       </c>
       <c r="H154">
-        <v>1079351350</v>
+        <v>1362400000</v>
       </c>
       <c r="I154">
-        <v>1079351350</v>
+        <v>1362400000</v>
       </c>
       <c r="J154">
         <v>100</v>
       </c>
       <c r="K154" t="str">
-        <v>유찰 1회</v>
+        <v>신건</v>
       </c>
       <c r="L154" t="str">
         <v>2026-06-15</v>
       </c>
       <c r="M154" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 일괄매각.  
-2. 건물 1층은 공부상 "연탄창고"로 기재되어 있으나 현황 주택으로 이용중임.
-3. 건물등기사항증명서 및 일반건축물대장에 부속건물인 단층 화장실이 기재되어 있으나 현황 소재불명으로 평가 및 매각에서 제외하고, 옥탑소재 제시외 건물(샷시조 함석지붕 계단실 약2㎡)도 평가 및 매각에서 제외함.</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B155" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C155" t="str">
-        <v>성남지원 2025타경53173</v>
-      </c>
-      <c r="D155" t="str">
-        <v>1</v>
-      </c>
-      <c r="E155" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 지2층407호</v>
-      </c>
-      <c r="F155">
-        <v>8.23</v>
-      </c>
-      <c r="G155">
-        <v>2.5</v>
-      </c>
-      <c r="H155">
-        <v>75000000</v>
-      </c>
-      <c r="I155">
-        <v>75000000</v>
-      </c>
-      <c r="J155">
-        <v>100</v>
-      </c>
-      <c r="K155" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L155" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M155" t="str">
-        <v>판매 및 영업시설로 이용중이며 벽체구분없는 오픈형 상가로 현재 공실상태임.</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B156" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C156" t="str">
-        <v>성남지원 2025타경53329</v>
-      </c>
-      <c r="D156" t="str">
-        <v>1</v>
-      </c>
-      <c r="E156" t="str">
-        <v>경기도 성남시 분당구 구미동 159 월드쇼핑(씨지브이 스퀘어) 1층시-153호</v>
-      </c>
-      <c r="F156">
-        <v>8.96</v>
-      </c>
-      <c r="G156">
-        <v>2.7</v>
-      </c>
-      <c r="H156">
-        <v>62000000</v>
-      </c>
-      <c r="I156">
-        <v>62000000</v>
-      </c>
-      <c r="J156">
-        <v>100</v>
-      </c>
-      <c r="K156" t="str">
-        <v>유찰 1회</v>
-      </c>
-      <c r="L156" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M156" t="str">
-        <v>본건 건물은 오픈형 상가로 벽체 구분없이 인접호수와 일체로 판매 및 영업시설(카페포토)로 이용중임.</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>성남 수정구</v>
-      </c>
-      <c r="B157" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C157" t="str">
-        <v>성남지원 2025타경53512</v>
-      </c>
-      <c r="D157" t="str">
-        <v>1</v>
-      </c>
-      <c r="E157" t="str">
-        <v>경기도 성남시 수정구 창곡동 559-6 라크리움 2층209호</v>
-      </c>
-      <c r="F157">
-        <v>73.5</v>
-      </c>
-      <c r="G157">
-        <v>22.2</v>
-      </c>
-      <c r="H157">
-        <v>561000000</v>
-      </c>
-      <c r="I157">
-        <v>561000000</v>
-      </c>
-      <c r="J157">
-        <v>100</v>
-      </c>
-      <c r="K157" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L157" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M157" t="str">
-        <v>건축물대장상 제2종근린생활시설(학원)으로 이용중이며, 현재 공실상태임.</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B158" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C158" t="str">
-        <v>성남지원 2025타경53550</v>
-      </c>
-      <c r="D158" t="str">
-        <v>1</v>
-      </c>
-      <c r="E158" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제2층 제205호</v>
-      </c>
-      <c r="F158">
-        <v>6.29</v>
-      </c>
-      <c r="G158">
-        <v>1.9</v>
-      </c>
-      <c r="H158">
-        <v>26200000</v>
-      </c>
-      <c r="I158">
-        <v>26200000</v>
-      </c>
-      <c r="J158">
-        <v>100</v>
-      </c>
-      <c r="K158" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L158" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M158" t="str">
-        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가로 현재 공실상태임.</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B159" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C159" t="str">
-        <v>성남지원 2025타경53676</v>
-      </c>
-      <c r="D159" t="str">
-        <v>1</v>
-      </c>
-      <c r="E159" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 제248호</v>
-      </c>
-      <c r="F159">
-        <v>6.99</v>
-      </c>
-      <c r="G159">
-        <v>2.1</v>
-      </c>
-      <c r="H159">
-        <v>48000000</v>
-      </c>
-      <c r="I159">
-        <v>48000000</v>
-      </c>
-      <c r="J159">
-        <v>100</v>
-      </c>
-      <c r="K159" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L159" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M159" t="str">
-        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가임.</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B160" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C160" t="str">
-        <v>성남지원 2025타경53690</v>
-      </c>
-      <c r="D160" t="str">
-        <v>1</v>
-      </c>
-      <c r="E160" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제지2층 제340호</v>
-      </c>
-      <c r="F160">
-        <v>6.9</v>
-      </c>
-      <c r="G160">
-        <v>2.1</v>
-      </c>
-      <c r="H160">
-        <v>51840000</v>
-      </c>
-      <c r="I160">
-        <v>51840000</v>
-      </c>
-      <c r="J160">
-        <v>100</v>
-      </c>
-      <c r="K160" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L160" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M160" t="str">
-        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가로 현재 공실상태임.</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B161" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C161" t="str">
-        <v>성남지원 2025타경53768</v>
-      </c>
-      <c r="D161" t="str">
-        <v>1</v>
-      </c>
-      <c r="E161" t="str">
-        <v>경기도 성남시 분당구 야탑동 341 성남(분당)여객자동차터미널및복합건물 제1층 제123호</v>
-      </c>
-      <c r="F161">
-        <v>5.28</v>
-      </c>
-      <c r="G161">
-        <v>1.6</v>
-      </c>
-      <c r="H161">
-        <v>47000000</v>
-      </c>
-      <c r="I161">
-        <v>47000000</v>
-      </c>
-      <c r="J161">
-        <v>100</v>
-      </c>
-      <c r="K161" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L161" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M161" t="str">
-        <v>판매 및 영업시설로 이용중이며, 벽체구분없는 오픈형 상가임.</v>
-      </c>
-    </row>
-    <row r="162" xml:space="preserve">
-      <c r="A162" t="str">
-        <v>성남 분당구</v>
-      </c>
-      <c r="B162" t="str">
-        <v>성남지원</v>
-      </c>
-      <c r="C162" t="str">
-        <v>성남지원 2025타경53798</v>
-      </c>
-      <c r="D162" t="str">
-        <v>1</v>
-      </c>
-      <c r="E162" t="str">
-        <v>경기도 성남시 분당구 서현동 183</v>
-      </c>
-      <c r="F162">
-        <v>655</v>
-      </c>
-      <c r="G162">
-        <v>198.1</v>
-      </c>
-      <c r="H162">
-        <v>1362400000</v>
-      </c>
-      <c r="I162">
-        <v>1362400000</v>
-      </c>
-      <c r="J162">
-        <v>100</v>
-      </c>
-      <c r="K162" t="str">
-        <v>신건</v>
-      </c>
-      <c r="L162" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="M162" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 본건 토지는 현황 '전'으로 이용중이고 맹지임. 농지취득자격증명서 제출요함(미제출시 보증금 몰수함)
 2. 토지의 정확한 위치나 면적, 인접 토지와의 경계측량등은 별도확인요망.</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M162"/>
+  <autoFilter ref="A1:M154"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M154"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7136,7 +6801,7 @@
         <v>해당 날짜에 예정된 물건</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-12</v>
+        <v>2026-06-15</v>
       </c>
     </row>
     <row r="3">
@@ -7172,7 +6837,7 @@
         <v>총 물건 수</v>
       </c>
       <c r="B5">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C5" t="str">
         <v>중복 제거 후</v>
